--- a/AAII_Financials/Quarterly/SNTG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNTG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>SNTG</t>
   </si>
@@ -2763,11 +2763,11 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
@@ -3658,11 +3658,11 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -5014,7 +5014,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
